--- a/docs/sample-output/02-podium-mixed-use-2-phase/estimate.xlsx
+++ b/docs/sample-output/02-podium-mixed-use-2-phase/estimate.xlsx
@@ -16,12 +16,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1294" uniqueCount="467">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1300" uniqueCount="472">
   <si>
     <t>FINISHES SOLUTIONS</t>
   </si>
   <si>
-    <t>Total Project Cost — Summary   ·   Station Square — podium mixed-use, 2 phases · Total $141,426,387</t>
+    <t>Total Project Cost — Summary   ·   Station Square — podium mixed-use, 2 phases · Total $140,902,626</t>
   </si>
   <si>
     <t>COST SUMMARY</t>
@@ -90,7 +90,7 @@
     <t>Research data version</t>
   </si>
   <si>
-    <t>2026.7c60a42879</t>
+    <t>2026.0c737c8255</t>
   </si>
   <si>
     <t>Engine</t>
@@ -99,10 +99,10 @@
     <t>budget-engine-2.0.0</t>
   </si>
   <si>
-    <t>All defaults come from the research data shipped with the app (2026.7c60a42879), escalated to the construction midpoint and adjusted to the project location. Values marked "Derived estimate — verify" have no direct published source.</t>
-  </si>
-  <si>
-    <t>Cost by Component   ·   Station Square — podium mixed-use, 2 phases · Total $141,426,387</t>
+    <t>All defaults come from the research data shipped with the app (2026.0c737c8255), escalated to the construction midpoint and adjusted to the project location. Values marked "Derived estimate — verify" have no direct published source.</t>
+  </si>
+  <si>
+    <t>Cost by Component   ·   Station Square — podium mixed-use, 2 phases · Total $140,902,626</t>
   </si>
   <si>
     <t>Component</t>
@@ -183,7 +183,7 @@
     <t>Residential over podium $11,375,504; Ground-floor retail $851,228</t>
   </si>
   <si>
-    <t>Cost by Phase   ·   Station Square — podium mixed-use, 2 phases · Total $141,426,387</t>
+    <t>Cost by Phase   ·   Station Square — podium mixed-use, 2 phases · Total $140,902,626</t>
   </si>
   <si>
     <t>Phase</t>
@@ -237,7 +237,7 @@
     <t>13.1%</t>
   </si>
   <si>
-    <t>Line-Item Detail   ·   Station Square — podium mixed-use, 2 phases · Total $141,426,387</t>
+    <t>Line-Item Detail   ·   Station Square — podium mixed-use, 2 phases · Total $140,902,626</t>
   </si>
   <si>
     <t>Group</t>
@@ -561,7 +561,7 @@
     <t>TOTAL</t>
   </si>
   <si>
-    <t>Draw Schedules   ·   Station Square — podium mixed-use, 2 phases · Total $141,426,387</t>
+    <t>Draw Schedules   ·   Station Square — podium mixed-use, 2 phases · Total $140,902,626</t>
   </si>
   <si>
     <t>PHASE 1 — PODIUM + RESIDENTIAL — MONTHLY DRAWS</t>
@@ -684,7 +684,7 @@
     <t>2030-02</t>
   </si>
   <si>
-    <t>Sources &amp; Assumptions   ·   Station Square — podium mixed-use, 2 phases · Total $141,426,387</t>
+    <t>Sources &amp; Assumptions   ·   Station Square — podium mixed-use, 2 phases · Total $140,902,626</t>
   </si>
   <si>
     <t>ASSUMPTIONS</t>
@@ -747,7 +747,7 @@
     <t>Phase 2 — retail fit-out — financing</t>
   </si>
   <si>
-    <t>SOURCES (57)</t>
+    <t>SOURCES (58)</t>
   </si>
   <si>
     <t>Ref</t>
@@ -1417,6 +1417,21 @@
   </si>
   <si>
     <t>225–410 USD/sf (2026)</t>
+  </si>
+  <si>
+    <t>residential/single-family.json#e10</t>
+  </si>
+  <si>
+    <t>Cost of Constructing a Home-2024 (Special Study for Housing Economics)</t>
+  </si>
+  <si>
+    <t>National Association of Home Builders (Eric Lynch)</t>
+  </si>
+  <si>
+    <t>26747 USD/unit (2024)</t>
+  </si>
+  <si>
+    <t>https://nahb.org/-/media/AB4EFC742624475A97A0A62189986FF8.ashx</t>
   </si>
 </sst>
 </file>
@@ -2006,7 +2021,7 @@
         <v>7</v>
       </c>
       <c r="B9" s="5">
-        <v>17881906.02</v>
+        <v>17881906.020000003</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
@@ -2014,7 +2029,7 @@
         <v>8</v>
       </c>
       <c r="B10" s="5">
-        <v>3995462.29</v>
+        <v>3541555.06</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
@@ -2022,7 +2037,7 @@
         <v>9</v>
       </c>
       <c r="B11" s="5">
-        <v>4870004.37</v>
+        <v>4850940.26</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
@@ -2030,7 +2045,7 @@
         <v>10</v>
       </c>
       <c r="B12" s="5">
-        <v>5083474</v>
+        <v>5055379.42</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
@@ -2038,7 +2053,7 @@
         <v>11</v>
       </c>
       <c r="B13" s="5">
-        <v>1088642.7</v>
+        <v>1065947.34</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
@@ -2046,7 +2061,7 @@
         <v>12</v>
       </c>
       <c r="B14" s="7">
-        <v>32919489.38</v>
+        <v>32395728.1</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
@@ -2062,7 +2077,7 @@
         <v>14</v>
       </c>
       <c r="B16" s="7">
-        <v>141426387.37</v>
+        <v>140902626.09</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
@@ -2101,7 +2116,7 @@
         <v>22</v>
       </c>
       <c r="B21" s="5">
-        <v>44195746.053125</v>
+        <v>44032070.653124996</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
@@ -2229,19 +2244,19 @@
         <v>93562265.73</v>
       </c>
       <c r="E5" s="13">
-        <v>30933724.09</v>
+        <v>30426477.61</v>
       </c>
       <c r="F5" s="13">
         <v>1237.29</v>
       </c>
       <c r="G5" s="13">
-        <v>124497227.11</v>
+        <v>123989980.63</v>
       </c>
       <c r="H5" s="13">
-        <v>444632.9539642857</v>
+        <v>442821.3593928571</v>
       </c>
       <c r="I5" s="14">
-        <v>423.45995615646257</v>
+        <v>421.73462799319725</v>
       </c>
       <c r="J5" s="12" t="s">
         <v>42</v>
@@ -2261,19 +2276,19 @@
         <v>5221832.26</v>
       </c>
       <c r="E6" s="13">
-        <v>1985765.29</v>
+        <v>1969250.49</v>
       </c>
       <c r="F6" s="13">
         <v>9721562.71</v>
       </c>
       <c r="G6" s="13">
-        <v>16929160.26</v>
+        <v>16912645.46</v>
       </c>
       <c r="H6" s="13">
-        <v>769.5072845454546</v>
+        <v>768.7566118181819</v>
       </c>
       <c r="I6" s="14">
-        <v>769.5072845454546</v>
+        <v>768.7566118181819</v>
       </c>
       <c r="J6" s="12" t="s">
         <v>46</v>
@@ -2289,13 +2304,13 @@
         <v>98784097.99</v>
       </c>
       <c r="E7" s="16">
-        <v>32919489.38</v>
+        <v>32395728.1</v>
       </c>
       <c r="F7" s="16">
         <v>9722800</v>
       </c>
       <c r="G7" s="16">
-        <v>141426387.37</v>
+        <v>140902626.09</v>
       </c>
       <c r="H7" s="15"/>
       <c r="I7" s="15"/>
@@ -2454,19 +2469,19 @@
         <v>94500744.83</v>
       </c>
       <c r="G5" s="13">
-        <v>31162076.05</v>
+        <v>30654741.74</v>
       </c>
       <c r="H5" s="13">
         <v>1237.29</v>
       </c>
       <c r="I5" s="13">
-        <v>125664058.17</v>
+        <v>125156723.86</v>
       </c>
       <c r="J5" s="13">
-        <v>75398434.9</v>
+        <v>75094034.32</v>
       </c>
       <c r="K5" s="13">
-        <v>3778567.14</v>
+        <v>3754230.76</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
@@ -2489,19 +2504,19 @@
         <v>4283353.16</v>
       </c>
       <c r="G6" s="13">
-        <v>1757413.33</v>
+        <v>1740986.36</v>
       </c>
       <c r="H6" s="13">
         <v>9721562.71</v>
       </c>
       <c r="I6" s="13">
-        <v>15762329.2</v>
+        <v>15745902.23</v>
       </c>
       <c r="J6" s="13">
-        <v>9457397.52</v>
+        <v>9447541.34</v>
       </c>
       <c r="K6" s="13">
-        <v>456348.53</v>
+        <v>455732.91</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
@@ -2516,13 +2531,13 @@
         <v>98784097.99</v>
       </c>
       <c r="G7" s="16">
-        <v>32919489.38</v>
+        <v>32395728.1</v>
       </c>
       <c r="H7" s="16">
         <v>9722800</v>
       </c>
       <c r="I7" s="16">
-        <v>141426387.37</v>
+        <v>140902626.09</v>
       </c>
       <c r="J7" s="15"/>
       <c r="K7" s="15"/>
@@ -4379,10 +4394,10 @@
         <v>163</v>
       </c>
       <c r="H65" s="14">
-        <v>4838.18</v>
+        <v>3407.22</v>
       </c>
       <c r="I65" s="13">
-        <v>812814.24</v>
+        <v>572412.96</v>
       </c>
       <c r="J65" s="12" t="s">
         <v>85</v>
@@ -4411,10 +4426,10 @@
         <v>163</v>
       </c>
       <c r="H66" s="14">
-        <v>4592.44</v>
+        <v>3407.22</v>
       </c>
       <c r="I66" s="13">
-        <v>771529.92</v>
+        <v>572412.96</v>
       </c>
       <c r="J66" s="12" t="s">
         <v>85</v>
@@ -5227,10 +5242,10 @@
         <v>163</v>
       </c>
       <c r="H93" s="14">
-        <v>4838.18</v>
+        <v>3407.22</v>
       </c>
       <c r="I93" s="13">
-        <v>26609.99</v>
+        <v>18739.71</v>
       </c>
       <c r="J93" s="12" t="s">
         <v>85</v>
@@ -5259,10 +5274,10 @@
         <v>163</v>
       </c>
       <c r="H94" s="14">
-        <v>4592.44</v>
+        <v>3407.22</v>
       </c>
       <c r="I94" s="13">
-        <v>25258.42</v>
+        <v>18739.71</v>
       </c>
       <c r="J94" s="12" t="s">
         <v>85</v>
@@ -5292,7 +5307,7 @@
       </c>
       <c r="H95" s="18"/>
       <c r="I95" s="13">
-        <v>1039411.14</v>
+        <v>1017435.23</v>
       </c>
       <c r="J95" s="12" t="s">
         <v>85</v>
@@ -5352,7 +5367,7 @@
       </c>
       <c r="H97" s="18"/>
       <c r="I97" s="13">
-        <v>42421.73</v>
+        <v>41702.28</v>
       </c>
       <c r="J97" s="12" t="s">
         <v>85</v>
@@ -5614,7 +5629,7 @@
       </c>
       <c r="H106" s="18"/>
       <c r="I106" s="13">
-        <v>4615597.1</v>
+        <v>4597137.33</v>
       </c>
       <c r="J106" s="12" t="s">
         <v>85</v>
@@ -5674,7 +5689,7 @@
       </c>
       <c r="H108" s="18"/>
       <c r="I108" s="13">
-        <v>211147.85</v>
+        <v>210543.51</v>
       </c>
       <c r="J108" s="12" t="s">
         <v>85</v>
@@ -5702,7 +5717,7 @@
       </c>
       <c r="H109" s="18"/>
       <c r="I109" s="13">
-        <v>3743481.93</v>
+        <v>3719232.85</v>
       </c>
       <c r="J109" s="12" t="s">
         <v>85</v>
@@ -5730,7 +5745,7 @@
       </c>
       <c r="H110" s="18"/>
       <c r="I110" s="13">
-        <v>35085.21</v>
+        <v>34997.91</v>
       </c>
       <c r="J110" s="12" t="s">
         <v>85</v>
@@ -5758,7 +5773,7 @@
       </c>
       <c r="H111" s="18"/>
       <c r="I111" s="13">
-        <v>746983.36</v>
+        <v>743939.88</v>
       </c>
       <c r="J111" s="12" t="s">
         <v>85</v>
@@ -5786,7 +5801,7 @@
       </c>
       <c r="H112" s="18"/>
       <c r="I112" s="13">
-        <v>7000.99</v>
+        <v>7000.46</v>
       </c>
       <c r="J112" s="12" t="s">
         <v>85</v>
@@ -5814,7 +5829,7 @@
       </c>
       <c r="H113" s="18"/>
       <c r="I113" s="13">
-        <v>456348.53</v>
+        <v>455732.91</v>
       </c>
       <c r="J113" s="12" t="s">
         <v>85</v>
@@ -5842,7 +5857,7 @@
       </c>
       <c r="H114" s="18"/>
       <c r="I114" s="13">
-        <v>94573.98</v>
+        <v>94475.41</v>
       </c>
       <c r="J114" s="12" t="s">
         <v>85</v>
@@ -5862,7 +5877,7 @@
       <c r="G115" s="15"/>
       <c r="H115" s="15"/>
       <c r="I115" s="16">
-        <v>141426387.37</v>
+        <v>140902626.09</v>
       </c>
       <c r="J115" s="15"/>
     </row>
@@ -5961,13 +5976,13 @@
         <v>0</v>
       </c>
       <c r="C6" s="13">
-        <v>13771977.69</v>
+        <v>13332459.45</v>
       </c>
       <c r="D6" s="13">
         <v>1237.29</v>
       </c>
       <c r="E6" s="13">
-        <v>14527199.33</v>
+        <v>14084637.08</v>
       </c>
       <c r="F6" s="13">
         <v>0</v>
@@ -5987,13 +6002,13 @@
         <v>372583.31</v>
       </c>
       <c r="C7" s="13">
-        <v>514301.86</v>
+        <v>512684.43</v>
       </c>
       <c r="D7" s="13">
         <v>0</v>
       </c>
       <c r="E7" s="13">
-        <v>886885.17</v>
+        <v>885267.74</v>
       </c>
       <c r="F7" s="13">
         <v>0</v>
@@ -6013,13 +6028,13 @@
         <v>1111874.07</v>
       </c>
       <c r="C8" s="13">
-        <v>514301.84</v>
+        <v>512684.42</v>
       </c>
       <c r="D8" s="13">
         <v>0</v>
       </c>
       <c r="E8" s="13">
-        <v>1626175.91</v>
+        <v>1624558.49</v>
       </c>
       <c r="F8" s="13">
         <v>0</v>
@@ -6039,13 +6054,13 @@
         <v>1833629.86</v>
       </c>
       <c r="C9" s="13">
-        <v>514301.84</v>
+        <v>512684.42</v>
       </c>
       <c r="D9" s="13">
         <v>0</v>
       </c>
       <c r="E9" s="13">
-        <v>2347931.7</v>
+        <v>2346314.28</v>
       </c>
       <c r="F9" s="13">
         <v>0</v>
@@ -6065,13 +6080,13 @@
         <v>2526468.24</v>
       </c>
       <c r="C10" s="13">
-        <v>514301.9</v>
+        <v>512684.47</v>
       </c>
       <c r="D10" s="13">
         <v>0</v>
       </c>
       <c r="E10" s="13">
-        <v>3040770.14</v>
+        <v>3039152.71</v>
       </c>
       <c r="F10" s="13">
         <v>0</v>
@@ -6091,13 +6106,13 @@
         <v>3179462.7</v>
       </c>
       <c r="C11" s="13">
-        <v>514301.89</v>
+        <v>512684.46</v>
       </c>
       <c r="D11" s="13">
         <v>0</v>
       </c>
       <c r="E11" s="13">
-        <v>3693764.59</v>
+        <v>3692147.16</v>
       </c>
       <c r="F11" s="13">
         <v>0</v>
@@ -6117,13 +6132,13 @@
         <v>3782315.13</v>
       </c>
       <c r="C12" s="13">
-        <v>514301.84</v>
+        <v>512684.42</v>
       </c>
       <c r="D12" s="13">
         <v>0</v>
       </c>
       <c r="E12" s="13">
-        <v>4296616.97</v>
+        <v>4294999.55</v>
       </c>
       <c r="F12" s="13">
         <v>0</v>
@@ -6143,13 +6158,13 @@
         <v>4325518.23</v>
       </c>
       <c r="C13" s="13">
-        <v>514301.94</v>
+        <v>512684.51</v>
       </c>
       <c r="D13" s="13">
         <v>0</v>
       </c>
       <c r="E13" s="13">
-        <v>4839820.17</v>
+        <v>4838202.74</v>
       </c>
       <c r="F13" s="13">
         <v>0</v>
@@ -6169,13 +6184,13 @@
         <v>4800505.3</v>
       </c>
       <c r="C14" s="13">
-        <v>514301.83</v>
+        <v>512684.41</v>
       </c>
       <c r="D14" s="13">
         <v>0</v>
       </c>
       <c r="E14" s="13">
-        <v>5314807.13</v>
+        <v>5313189.71</v>
       </c>
       <c r="F14" s="13">
         <v>0</v>
@@ -6195,13 +6210,13 @@
         <v>5199785.5</v>
       </c>
       <c r="C15" s="13">
-        <v>514301.83</v>
+        <v>512684.41</v>
       </c>
       <c r="D15" s="13">
         <v>0</v>
       </c>
       <c r="E15" s="13">
-        <v>5714087.33</v>
+        <v>5712469.91</v>
       </c>
       <c r="F15" s="13">
         <v>0</v>
@@ -6221,22 +6236,22 @@
         <v>5517062.01</v>
       </c>
       <c r="C16" s="13">
-        <v>514301.94</v>
+        <v>512684.51</v>
       </c>
       <c r="D16" s="13">
         <v>0</v>
       </c>
       <c r="E16" s="13">
-        <v>3977564.83</v>
+        <v>4231750.17</v>
       </c>
       <c r="F16" s="13">
-        <v>2053799.12</v>
+        <v>1797996.35</v>
       </c>
       <c r="G16" s="13">
         <v>0</v>
       </c>
       <c r="H16" s="13">
-        <v>2053799.12</v>
+        <v>1797996.35</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
@@ -6247,7 +6262,7 @@
         <v>5747331.16</v>
       </c>
       <c r="C17" s="13">
-        <v>514301.83</v>
+        <v>512684.41</v>
       </c>
       <c r="D17" s="13">
         <v>0</v>
@@ -6256,13 +6271,13 @@
         <v>0</v>
       </c>
       <c r="F17" s="13">
-        <v>6261632.99</v>
+        <v>6260015.57</v>
       </c>
       <c r="G17" s="13">
-        <v>11980.49</v>
+        <v>10488.31</v>
       </c>
       <c r="H17" s="13">
-        <v>8327412.6</v>
+        <v>8068500.23</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
@@ -6273,7 +6288,7 @@
         <v>5886961.48</v>
       </c>
       <c r="C18" s="13">
-        <v>514301.82</v>
+        <v>512684.4</v>
       </c>
       <c r="D18" s="13">
         <v>0</v>
@@ -6282,13 +6297,13 @@
         <v>0</v>
       </c>
       <c r="F18" s="13">
-        <v>6401263.3</v>
+        <v>6399645.88</v>
       </c>
       <c r="G18" s="13">
-        <v>48576.57</v>
+        <v>47066.25</v>
       </c>
       <c r="H18" s="13">
-        <v>14777252.47</v>
+        <v>14515212.36</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
@@ -6299,7 +6314,7 @@
         <v>5933750.89</v>
       </c>
       <c r="C19" s="13">
-        <v>514301.94</v>
+        <v>512684.51</v>
       </c>
       <c r="D19" s="13">
         <v>0</v>
@@ -6308,13 +6323,13 @@
         <v>0</v>
       </c>
       <c r="F19" s="13">
-        <v>6448052.83</v>
+        <v>6446435.4</v>
       </c>
       <c r="G19" s="13">
-        <v>86200.64</v>
+        <v>84672.07</v>
       </c>
       <c r="H19" s="13">
-        <v>21311505.94</v>
+        <v>21046319.83</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
@@ -6325,7 +6340,7 @@
         <v>5886961.49</v>
       </c>
       <c r="C20" s="13">
-        <v>514301.93</v>
+        <v>512684.5</v>
       </c>
       <c r="D20" s="13">
         <v>0</v>
@@ -6334,13 +6349,13 @@
         <v>0</v>
       </c>
       <c r="F20" s="13">
-        <v>6401263.42</v>
+        <v>6399645.99</v>
       </c>
       <c r="G20" s="13">
-        <v>124317.12</v>
+        <v>122770.2</v>
       </c>
       <c r="H20" s="13">
-        <v>27837086.48</v>
+        <v>27568736.02</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
@@ -6351,7 +6366,7 @@
         <v>5747331.16</v>
       </c>
       <c r="C21" s="13">
-        <v>514301.82</v>
+        <v>512684.4</v>
       </c>
       <c r="D21" s="13">
         <v>0</v>
@@ -6360,13 +6375,13 @@
         <v>0</v>
       </c>
       <c r="F21" s="13">
-        <v>6261632.98</v>
+        <v>6260015.56</v>
       </c>
       <c r="G21" s="13">
-        <v>162383</v>
+        <v>160817.63</v>
       </c>
       <c r="H21" s="13">
-        <v>34261102.46</v>
+        <v>33989569.21</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
@@ -6377,7 +6392,7 @@
         <v>5517062</v>
       </c>
       <c r="C22" s="13">
-        <v>514301.93</v>
+        <v>512684.5</v>
       </c>
       <c r="D22" s="13">
         <v>0</v>
@@ -6386,13 +6401,13 @@
         <v>0</v>
       </c>
       <c r="F22" s="13">
-        <v>6031363.93</v>
+        <v>6029746.5</v>
       </c>
       <c r="G22" s="13">
-        <v>199856.43</v>
+        <v>198272.49</v>
       </c>
       <c r="H22" s="13">
-        <v>40492322.82</v>
+        <v>40217588.2</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
@@ -6403,7 +6418,7 @@
         <v>5199785.51</v>
       </c>
       <c r="C23" s="13">
-        <v>514301.93</v>
+        <v>512684.5</v>
       </c>
       <c r="D23" s="13">
         <v>0</v>
@@ -6412,13 +6427,13 @@
         <v>0</v>
       </c>
       <c r="F23" s="13">
-        <v>5714087.44</v>
+        <v>5712470.01</v>
       </c>
       <c r="G23" s="13">
-        <v>236205.22</v>
+        <v>234602.6</v>
       </c>
       <c r="H23" s="13">
-        <v>46442615.48</v>
+        <v>46164660.81</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
@@ -6429,7 +6444,7 @@
         <v>4800505.28</v>
       </c>
       <c r="C24" s="13">
-        <v>514301.81</v>
+        <v>512684.39</v>
       </c>
       <c r="D24" s="13">
         <v>0</v>
@@ -6438,13 +6453,13 @@
         <v>0</v>
       </c>
       <c r="F24" s="13">
-        <v>5314807.09</v>
+        <v>5313189.67</v>
       </c>
       <c r="G24" s="13">
-        <v>270915.26</v>
+        <v>269293.85</v>
       </c>
       <c r="H24" s="13">
-        <v>52028337.83</v>
+        <v>51747144.33</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
@@ -6455,7 +6470,7 @@
         <v>4325518.22</v>
       </c>
       <c r="C25" s="13">
-        <v>514301.92</v>
+        <v>512684.49</v>
       </c>
       <c r="D25" s="13">
         <v>0</v>
@@ -6464,13 +6479,13 @@
         <v>0</v>
       </c>
       <c r="F25" s="13">
-        <v>4839820.14</v>
+        <v>4838202.71</v>
       </c>
       <c r="G25" s="13">
-        <v>303498.64</v>
+        <v>301858.34</v>
       </c>
       <c r="H25" s="13">
-        <v>57171656.61</v>
+        <v>56887205.38</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
@@ -6481,7 +6496,7 @@
         <v>3782315.13</v>
       </c>
       <c r="C26" s="13">
-        <v>514301.92</v>
+        <v>512684.49</v>
       </c>
       <c r="D26" s="13">
         <v>0</v>
@@ -6490,13 +6505,13 @@
         <v>0</v>
       </c>
       <c r="F26" s="13">
-        <v>4296617.05</v>
+        <v>4294999.62</v>
       </c>
       <c r="G26" s="13">
-        <v>333501.33</v>
+        <v>331842.03</v>
       </c>
       <c r="H26" s="13">
-        <v>61801774.99</v>
+        <v>61514047.03</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
@@ -6507,7 +6522,7 @@
         <v>3179462.7</v>
       </c>
       <c r="C27" s="13">
-        <v>514301.8</v>
+        <v>512684.37</v>
       </c>
       <c r="D27" s="13">
         <v>0</v>
@@ -6516,13 +6531,13 @@
         <v>0</v>
       </c>
       <c r="F27" s="13">
-        <v>3693764.5</v>
+        <v>3692147.07</v>
       </c>
       <c r="G27" s="13">
-        <v>360510.35</v>
+        <v>358831.94</v>
       </c>
       <c r="H27" s="13">
-        <v>65856049.84</v>
+        <v>65565026.04</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
@@ -6533,7 +6548,7 @@
         <v>2526468.23</v>
       </c>
       <c r="C28" s="13">
-        <v>514301.91</v>
+        <v>512684.47</v>
       </c>
       <c r="D28" s="13">
         <v>0</v>
@@ -6542,13 +6557,13 @@
         <v>0</v>
       </c>
       <c r="F28" s="13">
-        <v>3040770.14</v>
+        <v>3039152.7</v>
       </c>
       <c r="G28" s="13">
-        <v>384160.29</v>
+        <v>382462.65</v>
       </c>
       <c r="H28" s="13">
-        <v>69280980.27</v>
+        <v>68986641.39</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
@@ -6559,7 +6574,7 @@
         <v>1833629.86</v>
       </c>
       <c r="C29" s="13">
-        <v>514301.91</v>
+        <v>512684.47</v>
       </c>
       <c r="D29" s="13">
         <v>0</v>
@@ -6568,13 +6583,13 @@
         <v>0</v>
       </c>
       <c r="F29" s="13">
-        <v>2347931.77</v>
+        <v>2346314.33</v>
       </c>
       <c r="G29" s="13">
-        <v>404139.05</v>
+        <v>402422.07</v>
       </c>
       <c r="H29" s="13">
-        <v>72033051.09</v>
+        <v>71735377.79</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
@@ -6585,7 +6600,7 @@
         <v>1111874.04</v>
       </c>
       <c r="C30" s="13">
-        <v>514301.79</v>
+        <v>512684.36</v>
       </c>
       <c r="D30" s="13">
         <v>0</v>
@@ -6594,13 +6609,13 @@
         <v>0</v>
       </c>
       <c r="F30" s="13">
-        <v>1626175.83</v>
+        <v>1624558.4</v>
       </c>
       <c r="G30" s="13">
-        <v>420192.8</v>
+        <v>418456.37</v>
       </c>
       <c r="H30" s="13">
-        <v>74079419.72</v>
+        <v>73778392.56</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
@@ -6611,7 +6626,7 @@
         <v>372583.33</v>
       </c>
       <c r="C31" s="13">
-        <v>514301.9</v>
+        <v>512684.47</v>
       </c>
       <c r="D31" s="13">
         <v>0</v>
@@ -6620,13 +6635,13 @@
         <v>0</v>
       </c>
       <c r="F31" s="13">
-        <v>886885.23</v>
+        <v>885267.8</v>
       </c>
       <c r="G31" s="13">
-        <v>432129.95</v>
+        <v>430373.96</v>
       </c>
       <c r="H31" s="13">
-        <v>75398434.9</v>
+        <v>75094034.32</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
@@ -6675,22 +6690,22 @@
         <v>0</v>
       </c>
       <c r="C34" s="13">
-        <v>588652.87</v>
+        <v>574263.88</v>
       </c>
       <c r="D34" s="13">
         <v>9721562.71</v>
       </c>
       <c r="E34" s="13">
-        <v>6304931.68</v>
+        <v>6298360.89</v>
       </c>
       <c r="F34" s="13">
-        <v>4099857.88</v>
+        <v>4091941.11</v>
       </c>
       <c r="G34" s="13">
         <v>0</v>
       </c>
       <c r="H34" s="13">
-        <v>4099857.88</v>
+        <v>4091941.11</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
@@ -6701,7 +6716,7 @@
         <v>72975.86</v>
       </c>
       <c r="C35" s="13">
-        <v>51486.49</v>
+        <v>51376.18</v>
       </c>
       <c r="D35" s="13">
         <v>0</v>
@@ -6710,13 +6725,13 @@
         <v>0</v>
       </c>
       <c r="F35" s="13">
-        <v>124462.35</v>
+        <v>124352.04</v>
       </c>
       <c r="G35" s="13">
-        <v>23915.84</v>
+        <v>23869.66</v>
       </c>
       <c r="H35" s="13">
-        <v>4248236.07</v>
+        <v>4240162.81</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
@@ -6727,7 +6742,7 @@
         <v>213954.39</v>
       </c>
       <c r="C36" s="13">
-        <v>51486.49</v>
+        <v>51376.18</v>
       </c>
       <c r="D36" s="13">
         <v>0</v>
@@ -6736,13 +6751,13 @@
         <v>0</v>
       </c>
       <c r="F36" s="13">
-        <v>265440.88</v>
+        <v>265330.57</v>
       </c>
       <c r="G36" s="13">
-        <v>24781.38</v>
+        <v>24734.28</v>
       </c>
       <c r="H36" s="13">
-        <v>4538458.33</v>
+        <v>4530227.66</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
@@ -6753,7 +6768,7 @@
         <v>340352.29</v>
       </c>
       <c r="C37" s="13">
-        <v>51486.5</v>
+        <v>51376.19</v>
       </c>
       <c r="D37" s="13">
         <v>0</v>
@@ -6762,13 +6777,13 @@
         <v>0</v>
       </c>
       <c r="F37" s="13">
-        <v>391838.79</v>
+        <v>391728.48</v>
       </c>
       <c r="G37" s="13">
-        <v>26474.34</v>
+        <v>26426.33</v>
       </c>
       <c r="H37" s="13">
-        <v>4956771.46</v>
+        <v>4948382.47</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
@@ -6779,7 +6794,7 @@
         <v>443555.75</v>
       </c>
       <c r="C38" s="13">
-        <v>51486.49</v>
+        <v>51376.18</v>
       </c>
       <c r="D38" s="13">
         <v>0</v>
@@ -6788,13 +6803,13 @@
         <v>0</v>
       </c>
       <c r="F38" s="13">
-        <v>495042.24</v>
+        <v>494931.93</v>
       </c>
       <c r="G38" s="13">
-        <v>28914.5</v>
+        <v>28865.56</v>
       </c>
       <c r="H38" s="13">
-        <v>5480728.2</v>
+        <v>5472179.96</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
@@ -6805,7 +6820,7 @@
         <v>516531.6</v>
       </c>
       <c r="C39" s="13">
-        <v>51486.52</v>
+        <v>51376.2</v>
       </c>
       <c r="D39" s="13">
         <v>0</v>
@@ -6814,13 +6829,13 @@
         <v>0</v>
       </c>
       <c r="F39" s="13">
-        <v>568018.12</v>
+        <v>567907.8</v>
       </c>
       <c r="G39" s="13">
-        <v>31970.91</v>
+        <v>31921.05</v>
       </c>
       <c r="H39" s="13">
-        <v>6080717.23</v>
+        <v>6072008.81</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
@@ -6831,7 +6846,7 @@
         <v>554306.68</v>
       </c>
       <c r="C40" s="13">
-        <v>51486.47</v>
+        <v>51376.16</v>
       </c>
       <c r="D40" s="13">
         <v>0</v>
@@ -6840,13 +6855,13 @@
         <v>0</v>
       </c>
       <c r="F40" s="13">
-        <v>605793.15</v>
+        <v>605682.84</v>
       </c>
       <c r="G40" s="13">
-        <v>35470.85</v>
+        <v>35420.05</v>
       </c>
       <c r="H40" s="13">
-        <v>6721981.23</v>
+        <v>6713111.7</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
@@ -6857,7 +6872,7 @@
         <v>554306.68</v>
       </c>
       <c r="C41" s="13">
-        <v>51486.52</v>
+        <v>51376.2</v>
       </c>
       <c r="D41" s="13">
         <v>0</v>
@@ -6866,13 +6881,13 @@
         <v>0</v>
       </c>
       <c r="F41" s="13">
-        <v>605793.2</v>
+        <v>605682.88</v>
       </c>
       <c r="G41" s="13">
-        <v>39211.56</v>
+        <v>39159.82</v>
       </c>
       <c r="H41" s="13">
-        <v>7366985.99</v>
+        <v>7357954.4</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
@@ -6883,7 +6898,7 @@
         <v>516531.57</v>
       </c>
       <c r="C42" s="13">
-        <v>51486.47</v>
+        <v>51376.16</v>
       </c>
       <c r="D42" s="13">
         <v>0</v>
@@ -6892,13 +6907,13 @@
         <v>0</v>
       </c>
       <c r="F42" s="13">
-        <v>568018.04</v>
+        <v>567907.73</v>
       </c>
       <c r="G42" s="13">
-        <v>42974.08</v>
+        <v>42921.4</v>
       </c>
       <c r="H42" s="13">
-        <v>7977978.11</v>
+        <v>7968783.53</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
@@ -6909,7 +6924,7 @@
         <v>443555.78</v>
       </c>
       <c r="C43" s="13">
-        <v>51486.52</v>
+        <v>51376.2</v>
       </c>
       <c r="D43" s="13">
         <v>0</v>
@@ -6918,13 +6933,13 @@
         <v>0</v>
       </c>
       <c r="F43" s="13">
-        <v>495042.3</v>
+        <v>494931.98</v>
       </c>
       <c r="G43" s="13">
-        <v>46538.21</v>
+        <v>46484.57</v>
       </c>
       <c r="H43" s="13">
-        <v>8519558.62</v>
+        <v>8510200.08</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
@@ -6935,7 +6950,7 @@
         <v>340352.29</v>
       </c>
       <c r="C44" s="13">
-        <v>51486.52</v>
+        <v>51376.19</v>
       </c>
       <c r="D44" s="13">
         <v>0</v>
@@ -6944,13 +6959,13 @@
         <v>0</v>
       </c>
       <c r="F44" s="13">
-        <v>391838.81</v>
+        <v>391728.48</v>
       </c>
       <c r="G44" s="13">
-        <v>49697.43</v>
+        <v>49642.83</v>
       </c>
       <c r="H44" s="13">
-        <v>8961094.86</v>
+        <v>8951571.39</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.25">
@@ -6961,7 +6976,7 @@
         <v>213954.38</v>
       </c>
       <c r="C45" s="13">
-        <v>51486.44</v>
+        <v>51376.13</v>
       </c>
       <c r="D45" s="13">
         <v>0</v>
@@ -6970,13 +6985,13 @@
         <v>0</v>
       </c>
       <c r="F45" s="13">
-        <v>265440.82</v>
+        <v>265330.51</v>
       </c>
       <c r="G45" s="13">
-        <v>52273.05</v>
+        <v>52217.5</v>
       </c>
       <c r="H45" s="13">
-        <v>9278808.73</v>
+        <v>9269119.4</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
@@ -6987,7 +7002,7 @@
         <v>72975.89</v>
       </c>
       <c r="C46" s="13">
-        <v>51486.52</v>
+        <v>51376.19</v>
       </c>
       <c r="D46" s="13">
         <v>0</v>
@@ -6996,13 +7011,13 @@
         <v>0</v>
       </c>
       <c r="F46" s="13">
-        <v>124462.41</v>
+        <v>124352.08</v>
       </c>
       <c r="G46" s="13">
-        <v>54126.38</v>
+        <v>54069.86</v>
       </c>
       <c r="H46" s="13">
-        <v>9457397.52</v>
+        <v>9447541.34</v>
       </c>
     </row>
   </sheetData>
@@ -7025,7 +7040,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F73"/>
+  <dimension ref="A1:F74"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="34" customWidth="1"/>
@@ -8310,6 +8325,26 @@
       </c>
       <c r="F73" s="12" t="s">
         <v>405</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A74" s="11" t="s">
+        <v>467</v>
+      </c>
+      <c r="B74" s="12" t="s">
+        <v>468</v>
+      </c>
+      <c r="C74" s="12" t="s">
+        <v>469</v>
+      </c>
+      <c r="D74" s="12" t="s">
+        <v>470</v>
+      </c>
+      <c r="E74" s="12" t="s">
+        <v>254</v>
+      </c>
+      <c r="F74" s="12" t="s">
+        <v>471</v>
       </c>
     </row>
   </sheetData>

--- a/docs/sample-output/02-podium-mixed-use-2-phase/estimate.xlsx
+++ b/docs/sample-output/02-podium-mixed-use-2-phase/estimate.xlsx
@@ -21,7 +21,7 @@
     <t>FINISHES SOLUTIONS</t>
   </si>
   <si>
-    <t>Total Project Cost — Summary   ·   Station Square — podium mixed-use, 2 phases · Total $140,902,626</t>
+    <t>Total Project Cost — Summary   ·   Station Square — podium mixed-use, 2 phases · Total $141,142,304</t>
   </si>
   <si>
     <t>COST SUMMARY</t>
@@ -102,7 +102,7 @@
     <t>All defaults come from the research data shipped with the app (2026.0c737c8255), escalated to the construction midpoint and adjusted to the project location. Values marked "Derived estimate — verify" have no direct published source.</t>
   </si>
   <si>
-    <t>Cost by Component   ·   Station Square — podium mixed-use, 2 phases · Total $140,902,626</t>
+    <t>Cost by Component   ·   Station Square — podium mixed-use, 2 phases · Total $141,142,304</t>
   </si>
   <si>
     <t>Component</t>
@@ -183,7 +183,7 @@
     <t>Residential over podium $11,375,504; Ground-floor retail $851,228</t>
   </si>
   <si>
-    <t>Cost by Phase   ·   Station Square — podium mixed-use, 2 phases · Total $140,902,626</t>
+    <t>Cost by Phase   ·   Station Square — podium mixed-use, 2 phases · Total $141,142,304</t>
   </si>
   <si>
     <t>Phase</t>
@@ -237,7 +237,7 @@
     <t>13.1%</t>
   </si>
   <si>
-    <t>Line-Item Detail   ·   Station Square — podium mixed-use, 2 phases · Total $140,902,626</t>
+    <t>Line-Item Detail   ·   Station Square — podium mixed-use, 2 phases · Total $141,142,304</t>
   </si>
   <si>
     <t>Group</t>
@@ -561,7 +561,7 @@
     <t>TOTAL</t>
   </si>
   <si>
-    <t>Draw Schedules   ·   Station Square — podium mixed-use, 2 phases · Total $140,902,626</t>
+    <t>Draw Schedules   ·   Station Square — podium mixed-use, 2 phases · Total $141,142,304</t>
   </si>
   <si>
     <t>PHASE 1 — PODIUM + RESIDENTIAL — MONTHLY DRAWS</t>
@@ -684,7 +684,7 @@
     <t>2030-02</t>
   </si>
   <si>
-    <t>Sources &amp; Assumptions   ·   Station Square — podium mixed-use, 2 phases · Total $140,902,626</t>
+    <t>Sources &amp; Assumptions   ·   Station Square — podium mixed-use, 2 phases · Total $141,142,304</t>
   </si>
   <si>
     <t>ASSUMPTIONS</t>
@@ -2021,7 +2021,7 @@
         <v>7</v>
       </c>
       <c r="B9" s="5">
-        <v>17881906.020000003</v>
+        <v>17987218.360000003</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
@@ -2037,7 +2037,7 @@
         <v>9</v>
       </c>
       <c r="B11" s="5">
-        <v>4850940.26</v>
+        <v>4855152.75</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
@@ -2045,7 +2045,7 @@
         <v>10</v>
       </c>
       <c r="B12" s="5">
-        <v>5055379.42</v>
+        <v>5185532.45</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
@@ -2061,7 +2061,7 @@
         <v>12</v>
       </c>
       <c r="B14" s="7">
-        <v>32395728.1</v>
+        <v>32635405.96</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
@@ -2077,7 +2077,7 @@
         <v>14</v>
       </c>
       <c r="B16" s="7">
-        <v>140902626.09</v>
+        <v>141142303.95</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
@@ -2116,7 +2116,7 @@
         <v>22</v>
       </c>
       <c r="B21" s="5">
-        <v>44032070.653124996</v>
+        <v>44106969.98437499</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
@@ -2244,19 +2244,19 @@
         <v>93562265.73</v>
       </c>
       <c r="E5" s="13">
-        <v>30426477.61</v>
+        <v>31185996.9</v>
       </c>
       <c r="F5" s="13">
-        <v>1237.29</v>
+        <v>9045896.2</v>
       </c>
       <c r="G5" s="13">
-        <v>123989980.63</v>
+        <v>133794158.83</v>
       </c>
       <c r="H5" s="13">
-        <v>442821.3593928571</v>
+        <v>477836.2815357143</v>
       </c>
       <c r="I5" s="14">
-        <v>421.73462799319725</v>
+        <v>455.08217289115646</v>
       </c>
       <c r="J5" s="12" t="s">
         <v>42</v>
@@ -2276,19 +2276,19 @@
         <v>5221832.26</v>
       </c>
       <c r="E6" s="13">
-        <v>1969250.49</v>
+        <v>1449409.06</v>
       </c>
       <c r="F6" s="13">
-        <v>9721562.71</v>
+        <v>676903.8</v>
       </c>
       <c r="G6" s="13">
-        <v>16912645.46</v>
+        <v>7348145.12</v>
       </c>
       <c r="H6" s="13">
-        <v>768.7566118181819</v>
+        <v>334.0065963636364</v>
       </c>
       <c r="I6" s="14">
-        <v>768.7566118181819</v>
+        <v>334.0065963636364</v>
       </c>
       <c r="J6" s="12" t="s">
         <v>46</v>
@@ -2304,13 +2304,13 @@
         <v>98784097.99</v>
       </c>
       <c r="E7" s="16">
-        <v>32395728.1</v>
+        <v>32635405.96</v>
       </c>
       <c r="F7" s="16">
         <v>9722800</v>
       </c>
       <c r="G7" s="16">
-        <v>140902626.09</v>
+        <v>141142303.95</v>
       </c>
       <c r="H7" s="15"/>
       <c r="I7" s="15"/>
@@ -2469,19 +2469,19 @@
         <v>94500744.83</v>
       </c>
       <c r="G5" s="13">
-        <v>30654741.74</v>
+        <v>31416036.58</v>
       </c>
       <c r="H5" s="13">
-        <v>1237.29</v>
+        <v>9045896.2</v>
       </c>
       <c r="I5" s="13">
-        <v>125156723.86</v>
+        <v>134962677.61</v>
       </c>
       <c r="J5" s="13">
-        <v>75094034.32</v>
+        <v>80977606.57</v>
       </c>
       <c r="K5" s="13">
-        <v>3754230.76</v>
+        <v>4246065.2</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
@@ -2504,19 +2504,19 @@
         <v>4283353.16</v>
       </c>
       <c r="G6" s="13">
-        <v>1740986.36</v>
+        <v>1219369.38</v>
       </c>
       <c r="H6" s="13">
-        <v>9721562.71</v>
+        <v>676903.8</v>
       </c>
       <c r="I6" s="13">
-        <v>15745902.23</v>
+        <v>6179626.34</v>
       </c>
       <c r="J6" s="13">
-        <v>9447541.34</v>
+        <v>3707775.8</v>
       </c>
       <c r="K6" s="13">
-        <v>455732.91</v>
+        <v>92613.42</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
@@ -2531,13 +2531,13 @@
         <v>98784097.99</v>
       </c>
       <c r="G7" s="16">
-        <v>32395728.1</v>
+        <v>32635405.96</v>
       </c>
       <c r="H7" s="16">
         <v>9722800</v>
       </c>
       <c r="I7" s="16">
-        <v>140902626.09</v>
+        <v>141142303.95</v>
       </c>
       <c r="J7" s="15"/>
       <c r="K7" s="15"/>
@@ -5395,7 +5395,7 @@
       </c>
       <c r="H98" s="18"/>
       <c r="I98" s="13">
-        <v>1208.94</v>
+        <v>8838607.59</v>
       </c>
       <c r="J98" s="12" t="s">
         <v>85</v>
@@ -5423,7 +5423,7 @@
       </c>
       <c r="H99" s="18"/>
       <c r="I99" s="13">
-        <v>9498791.06</v>
+        <v>661392.41</v>
       </c>
       <c r="J99" s="12" t="s">
         <v>85</v>
@@ -5451,7 +5451,7 @@
       </c>
       <c r="H100" s="18"/>
       <c r="I100" s="13">
-        <v>24.18</v>
+        <v>176772.15</v>
       </c>
       <c r="J100" s="12" t="s">
         <v>85</v>
@@ -5479,7 +5479,7 @@
       </c>
       <c r="H101" s="18"/>
       <c r="I101" s="13">
-        <v>189975.82</v>
+        <v>13227.85</v>
       </c>
       <c r="J101" s="12" t="s">
         <v>85</v>
@@ -5507,7 +5507,7 @@
       </c>
       <c r="H102" s="18"/>
       <c r="I102" s="13">
-        <v>4.17</v>
+        <v>30516.46</v>
       </c>
       <c r="J102" s="12" t="s">
         <v>85</v>
@@ -5535,7 +5535,7 @@
       </c>
       <c r="H103" s="18"/>
       <c r="I103" s="13">
-        <v>32795.83</v>
+        <v>2283.54</v>
       </c>
       <c r="J103" s="12" t="s">
         <v>85</v>
@@ -5564,10 +5564,10 @@
         <v>173</v>
       </c>
       <c r="H104" s="14">
-        <v>13.29834</v>
+        <v>97224.68349</v>
       </c>
       <c r="I104" s="13">
-        <v>27.7</v>
+        <v>202551.42</v>
       </c>
       <c r="J104" s="12" t="s">
         <v>85</v>
@@ -5596,10 +5596,10 @@
         <v>173</v>
       </c>
       <c r="H105" s="14">
-        <v>104486.70166</v>
+        <v>7275.31651</v>
       </c>
       <c r="I105" s="13">
-        <v>104486.7</v>
+        <v>7275.32</v>
       </c>
       <c r="J105" s="12" t="s">
         <v>85</v>
@@ -5629,7 +5629,7 @@
       </c>
       <c r="H106" s="18"/>
       <c r="I106" s="13">
-        <v>4597137.33</v>
+        <v>4605238.28</v>
       </c>
       <c r="J106" s="12" t="s">
         <v>85</v>
@@ -5689,7 +5689,7 @@
       </c>
       <c r="H108" s="18"/>
       <c r="I108" s="13">
-        <v>210543.51</v>
+        <v>206655.05</v>
       </c>
       <c r="J108" s="12" t="s">
         <v>85</v>
@@ -5717,7 +5717,7 @@
       </c>
       <c r="H109" s="18"/>
       <c r="I109" s="13">
-        <v>3719232.85</v>
+        <v>4209302.39</v>
       </c>
       <c r="J109" s="12" t="s">
         <v>85</v>
@@ -5745,7 +5745,7 @@
       </c>
       <c r="H110" s="18"/>
       <c r="I110" s="13">
-        <v>34997.91</v>
+        <v>36762.81</v>
       </c>
       <c r="J110" s="12" t="s">
         <v>85</v>
@@ -5773,7 +5773,7 @@
       </c>
       <c r="H111" s="18"/>
       <c r="I111" s="13">
-        <v>743939.88</v>
+        <v>802764.96</v>
       </c>
       <c r="J111" s="12" t="s">
         <v>85</v>
@@ -5801,7 +5801,7 @@
       </c>
       <c r="H112" s="18"/>
       <c r="I112" s="13">
-        <v>7000.46</v>
+        <v>7011.11</v>
       </c>
       <c r="J112" s="12" t="s">
         <v>85</v>
@@ -5829,7 +5829,7 @@
       </c>
       <c r="H113" s="18"/>
       <c r="I113" s="13">
-        <v>455732.91</v>
+        <v>92613.42</v>
       </c>
       <c r="J113" s="12" t="s">
         <v>85</v>
@@ -5857,7 +5857,7 @@
       </c>
       <c r="H114" s="18"/>
       <c r="I114" s="13">
-        <v>94475.41</v>
+        <v>37077.76</v>
       </c>
       <c r="J114" s="12" t="s">
         <v>85</v>
@@ -5877,7 +5877,7 @@
       <c r="G115" s="15"/>
       <c r="H115" s="15"/>
       <c r="I115" s="16">
-        <v>140902626.09</v>
+        <v>141142303.95</v>
       </c>
       <c r="J115" s="15"/>
     </row>
@@ -5979,10 +5979,10 @@
         <v>13332459.45</v>
       </c>
       <c r="D6" s="13">
-        <v>1237.29</v>
+        <v>9045896.2</v>
       </c>
       <c r="E6" s="13">
-        <v>14084637.08</v>
+        <v>23188131.72</v>
       </c>
       <c r="F6" s="13">
         <v>0</v>
@@ -6002,13 +6002,13 @@
         <v>372583.31</v>
       </c>
       <c r="C7" s="13">
-        <v>512684.43</v>
+        <v>521109.42</v>
       </c>
       <c r="D7" s="13">
         <v>0</v>
       </c>
       <c r="E7" s="13">
-        <v>885267.74</v>
+        <v>893692.73</v>
       </c>
       <c r="F7" s="13">
         <v>0</v>
@@ -6028,13 +6028,13 @@
         <v>1111874.07</v>
       </c>
       <c r="C8" s="13">
-        <v>512684.42</v>
+        <v>521109.41</v>
       </c>
       <c r="D8" s="13">
         <v>0</v>
       </c>
       <c r="E8" s="13">
-        <v>1624558.49</v>
+        <v>1632983.48</v>
       </c>
       <c r="F8" s="13">
         <v>0</v>
@@ -6054,13 +6054,13 @@
         <v>1833629.86</v>
       </c>
       <c r="C9" s="13">
-        <v>512684.42</v>
+        <v>521109.41</v>
       </c>
       <c r="D9" s="13">
         <v>0</v>
       </c>
       <c r="E9" s="13">
-        <v>2346314.28</v>
+        <v>2354739.27</v>
       </c>
       <c r="F9" s="13">
         <v>0</v>
@@ -6080,13 +6080,13 @@
         <v>2526468.24</v>
       </c>
       <c r="C10" s="13">
-        <v>512684.47</v>
+        <v>521109.46</v>
       </c>
       <c r="D10" s="13">
         <v>0</v>
       </c>
       <c r="E10" s="13">
-        <v>3039152.71</v>
+        <v>3047577.7</v>
       </c>
       <c r="F10" s="13">
         <v>0</v>
@@ -6106,13 +6106,13 @@
         <v>3179462.7</v>
       </c>
       <c r="C11" s="13">
-        <v>512684.46</v>
+        <v>521109.45</v>
       </c>
       <c r="D11" s="13">
         <v>0</v>
       </c>
       <c r="E11" s="13">
-        <v>3692147.16</v>
+        <v>3700572.15</v>
       </c>
       <c r="F11" s="13">
         <v>0</v>
@@ -6132,13 +6132,13 @@
         <v>3782315.13</v>
       </c>
       <c r="C12" s="13">
-        <v>512684.42</v>
+        <v>521109.41</v>
       </c>
       <c r="D12" s="13">
         <v>0</v>
       </c>
       <c r="E12" s="13">
-        <v>4294999.55</v>
+        <v>4303424.54</v>
       </c>
       <c r="F12" s="13">
         <v>0</v>
@@ -6158,13 +6158,13 @@
         <v>4325518.23</v>
       </c>
       <c r="C13" s="13">
-        <v>512684.51</v>
+        <v>521109.5</v>
       </c>
       <c r="D13" s="13">
         <v>0</v>
       </c>
       <c r="E13" s="13">
-        <v>4838202.74</v>
+        <v>4846627.73</v>
       </c>
       <c r="F13" s="13">
         <v>0</v>
@@ -6184,13 +6184,13 @@
         <v>4800505.3</v>
       </c>
       <c r="C14" s="13">
-        <v>512684.41</v>
+        <v>521109.39</v>
       </c>
       <c r="D14" s="13">
         <v>0</v>
       </c>
       <c r="E14" s="13">
-        <v>5313189.71</v>
+        <v>5321614.69</v>
       </c>
       <c r="F14" s="13">
         <v>0</v>
@@ -6210,22 +6210,22 @@
         <v>5199785.5</v>
       </c>
       <c r="C15" s="13">
-        <v>512684.41</v>
+        <v>521109.39</v>
       </c>
       <c r="D15" s="13">
         <v>0</v>
       </c>
       <c r="E15" s="13">
-        <v>5712469.91</v>
+        <v>4695707.03</v>
       </c>
       <c r="F15" s="13">
-        <v>0</v>
+        <v>1025187.86</v>
       </c>
       <c r="G15" s="13">
         <v>0</v>
       </c>
       <c r="H15" s="13">
-        <v>0</v>
+        <v>1025187.86</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
@@ -6236,22 +6236,22 @@
         <v>5517062.01</v>
       </c>
       <c r="C16" s="13">
-        <v>512684.51</v>
+        <v>521109.5</v>
       </c>
       <c r="D16" s="13">
         <v>0</v>
       </c>
       <c r="E16" s="13">
-        <v>4231750.17</v>
+        <v>0</v>
       </c>
       <c r="F16" s="13">
-        <v>1797996.35</v>
+        <v>6038171.51</v>
       </c>
       <c r="G16" s="13">
-        <v>0</v>
+        <v>5980.26</v>
       </c>
       <c r="H16" s="13">
-        <v>1797996.35</v>
+        <v>7069339.63</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
@@ -6262,7 +6262,7 @@
         <v>5747331.16</v>
       </c>
       <c r="C17" s="13">
-        <v>512684.41</v>
+        <v>521109.39</v>
       </c>
       <c r="D17" s="13">
         <v>0</v>
@@ -6271,13 +6271,13 @@
         <v>0</v>
       </c>
       <c r="F17" s="13">
-        <v>6260015.57</v>
+        <v>6268440.55</v>
       </c>
       <c r="G17" s="13">
-        <v>10488.31</v>
+        <v>41237.81</v>
       </c>
       <c r="H17" s="13">
-        <v>8068500.23</v>
+        <v>13379017.99</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
@@ -6288,7 +6288,7 @@
         <v>5886961.48</v>
       </c>
       <c r="C18" s="13">
-        <v>512684.4</v>
+        <v>521109.39</v>
       </c>
       <c r="D18" s="13">
         <v>0</v>
@@ -6297,13 +6297,13 @@
         <v>0</v>
       </c>
       <c r="F18" s="13">
-        <v>6399645.88</v>
+        <v>6408070.87</v>
       </c>
       <c r="G18" s="13">
-        <v>47066.25</v>
+        <v>78044.27</v>
       </c>
       <c r="H18" s="13">
-        <v>14515212.36</v>
+        <v>19865133.13</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
@@ -6314,7 +6314,7 @@
         <v>5933750.89</v>
       </c>
       <c r="C19" s="13">
-        <v>512684.51</v>
+        <v>521109.5</v>
       </c>
       <c r="D19" s="13">
         <v>0</v>
@@ -6323,13 +6323,13 @@
         <v>0</v>
       </c>
       <c r="F19" s="13">
-        <v>6446435.4</v>
+        <v>6454860.39</v>
       </c>
       <c r="G19" s="13">
-        <v>84672.07</v>
+        <v>115879.94</v>
       </c>
       <c r="H19" s="13">
-        <v>21046319.83</v>
+        <v>26435873.46</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
@@ -6340,7 +6340,7 @@
         <v>5886961.49</v>
       </c>
       <c r="C20" s="13">
-        <v>512684.5</v>
+        <v>521109.48</v>
       </c>
       <c r="D20" s="13">
         <v>0</v>
@@ -6349,13 +6349,13 @@
         <v>0</v>
       </c>
       <c r="F20" s="13">
-        <v>6399645.99</v>
+        <v>6408070.97</v>
       </c>
       <c r="G20" s="13">
-        <v>122770.2</v>
+        <v>154209.26</v>
       </c>
       <c r="H20" s="13">
-        <v>27568736.02</v>
+        <v>32998153.69</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
@@ -6366,7 +6366,7 @@
         <v>5747331.16</v>
       </c>
       <c r="C21" s="13">
-        <v>512684.4</v>
+        <v>521109.39</v>
       </c>
       <c r="D21" s="13">
         <v>0</v>
@@ -6375,13 +6375,13 @@
         <v>0</v>
       </c>
       <c r="F21" s="13">
-        <v>6260015.56</v>
+        <v>6268440.55</v>
       </c>
       <c r="G21" s="13">
-        <v>160817.63</v>
+        <v>192489.23</v>
       </c>
       <c r="H21" s="13">
-        <v>33989569.21</v>
+        <v>39459083.47</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
@@ -6392,7 +6392,7 @@
         <v>5517062</v>
       </c>
       <c r="C22" s="13">
-        <v>512684.5</v>
+        <v>521109.48</v>
       </c>
       <c r="D22" s="13">
         <v>0</v>
@@ -6401,13 +6401,13 @@
         <v>0</v>
       </c>
       <c r="F22" s="13">
-        <v>6029746.5</v>
+        <v>6038171.48</v>
       </c>
       <c r="G22" s="13">
-        <v>198272.49</v>
+        <v>230177.99</v>
       </c>
       <c r="H22" s="13">
-        <v>40217588.2</v>
+        <v>45727432.94</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
@@ -6418,7 +6418,7 @@
         <v>5199785.51</v>
       </c>
       <c r="C23" s="13">
-        <v>512684.5</v>
+        <v>521109.48</v>
       </c>
       <c r="D23" s="13">
         <v>0</v>
@@ -6427,13 +6427,13 @@
         <v>0</v>
       </c>
       <c r="F23" s="13">
-        <v>5712470.01</v>
+        <v>5720894.99</v>
       </c>
       <c r="G23" s="13">
-        <v>234602.6</v>
+        <v>266743.36</v>
       </c>
       <c r="H23" s="13">
-        <v>46164660.81</v>
+        <v>51715071.29</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
@@ -6444,7 +6444,7 @@
         <v>4800505.28</v>
       </c>
       <c r="C24" s="13">
-        <v>512684.39</v>
+        <v>521109.38</v>
       </c>
       <c r="D24" s="13">
         <v>0</v>
@@ -6453,13 +6453,13 @@
         <v>0</v>
       </c>
       <c r="F24" s="13">
-        <v>5313189.67</v>
+        <v>5321614.66</v>
       </c>
       <c r="G24" s="13">
-        <v>269293.85</v>
+        <v>301671.25</v>
       </c>
       <c r="H24" s="13">
-        <v>51747144.33</v>
+        <v>57338357.2</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
@@ -6470,7 +6470,7 @@
         <v>4325518.22</v>
       </c>
       <c r="C25" s="13">
-        <v>512684.49</v>
+        <v>521109.47</v>
       </c>
       <c r="D25" s="13">
         <v>0</v>
@@ -6479,13 +6479,13 @@
         <v>0</v>
       </c>
       <c r="F25" s="13">
-        <v>4838202.71</v>
+        <v>4846627.69</v>
       </c>
       <c r="G25" s="13">
-        <v>301858.34</v>
+        <v>334473.75</v>
       </c>
       <c r="H25" s="13">
-        <v>56887205.38</v>
+        <v>62519458.64</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
@@ -6496,7 +6496,7 @@
         <v>3782315.13</v>
       </c>
       <c r="C26" s="13">
-        <v>512684.49</v>
+        <v>521109.47</v>
       </c>
       <c r="D26" s="13">
         <v>0</v>
@@ -6505,13 +6505,13 @@
         <v>0</v>
       </c>
       <c r="F26" s="13">
-        <v>4294999.62</v>
+        <v>4303424.6</v>
       </c>
       <c r="G26" s="13">
-        <v>331842.03</v>
+        <v>364696.84</v>
       </c>
       <c r="H26" s="13">
-        <v>61514047.03</v>
+        <v>67187580.08</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
@@ -6522,7 +6522,7 @@
         <v>3179462.7</v>
       </c>
       <c r="C27" s="13">
-        <v>512684.37</v>
+        <v>521109.36</v>
       </c>
       <c r="D27" s="13">
         <v>0</v>
@@ -6531,13 +6531,13 @@
         <v>0</v>
       </c>
       <c r="F27" s="13">
-        <v>3692147.07</v>
+        <v>3700572.06</v>
       </c>
       <c r="G27" s="13">
-        <v>358831.94</v>
+        <v>391927.55</v>
       </c>
       <c r="H27" s="13">
-        <v>65565026.04</v>
+        <v>71280079.69</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
@@ -6548,7 +6548,7 @@
         <v>2526468.23</v>
       </c>
       <c r="C28" s="13">
-        <v>512684.47</v>
+        <v>521109.46</v>
       </c>
       <c r="D28" s="13">
         <v>0</v>
@@ -6557,13 +6557,13 @@
         <v>0</v>
       </c>
       <c r="F28" s="13">
-        <v>3039152.7</v>
+        <v>3047577.69</v>
       </c>
       <c r="G28" s="13">
-        <v>382462.65</v>
+        <v>415800.46</v>
       </c>
       <c r="H28" s="13">
-        <v>68986641.39</v>
+        <v>74743457.84</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
@@ -6574,7 +6574,7 @@
         <v>1833629.86</v>
       </c>
       <c r="C29" s="13">
-        <v>512684.47</v>
+        <v>521109.46</v>
       </c>
       <c r="D29" s="13">
         <v>0</v>
@@ -6583,13 +6583,13 @@
         <v>0</v>
       </c>
       <c r="F29" s="13">
-        <v>2346314.33</v>
+        <v>2354739.32</v>
       </c>
       <c r="G29" s="13">
-        <v>402422.07</v>
+        <v>436003.5</v>
       </c>
       <c r="H29" s="13">
-        <v>71735377.79</v>
+        <v>77534200.66</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
@@ -6600,7 +6600,7 @@
         <v>1111874.04</v>
       </c>
       <c r="C30" s="13">
-        <v>512684.36</v>
+        <v>521109.35</v>
       </c>
       <c r="D30" s="13">
         <v>0</v>
@@ -6609,13 +6609,13 @@
         <v>0</v>
       </c>
       <c r="F30" s="13">
-        <v>1624558.4</v>
+        <v>1632983.39</v>
       </c>
       <c r="G30" s="13">
-        <v>418456.37</v>
+        <v>452282.84</v>
       </c>
       <c r="H30" s="13">
-        <v>73778392.56</v>
+        <v>79619466.89</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
@@ -6626,7 +6626,7 @@
         <v>372583.33</v>
       </c>
       <c r="C31" s="13">
-        <v>512684.47</v>
+        <v>521109.46</v>
       </c>
       <c r="D31" s="13">
         <v>0</v>
@@ -6635,13 +6635,13 @@
         <v>0</v>
       </c>
       <c r="F31" s="13">
-        <v>885267.8</v>
+        <v>893692.79</v>
       </c>
       <c r="G31" s="13">
-        <v>430373.96</v>
+        <v>464446.89</v>
       </c>
       <c r="H31" s="13">
-        <v>75094034.32</v>
+        <v>80977606.57</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
@@ -6693,19 +6693,19 @@
         <v>574263.88</v>
       </c>
       <c r="D34" s="13">
-        <v>9721562.71</v>
+        <v>676903.8</v>
       </c>
       <c r="E34" s="13">
-        <v>6298360.89</v>
+        <v>1288245.44</v>
       </c>
       <c r="F34" s="13">
-        <v>4091941.11</v>
+        <v>0</v>
       </c>
       <c r="G34" s="13">
         <v>0</v>
       </c>
       <c r="H34" s="13">
-        <v>4091941.11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
@@ -6716,22 +6716,22 @@
         <v>72975.86</v>
       </c>
       <c r="C35" s="13">
-        <v>51376.18</v>
+        <v>42951.2</v>
       </c>
       <c r="D35" s="13">
         <v>0</v>
       </c>
       <c r="E35" s="13">
-        <v>0</v>
+        <v>115927.06</v>
       </c>
       <c r="F35" s="13">
-        <v>124352.04</v>
+        <v>0</v>
       </c>
       <c r="G35" s="13">
-        <v>23869.66</v>
+        <v>0</v>
       </c>
       <c r="H35" s="13">
-        <v>4240162.81</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
@@ -6742,22 +6742,22 @@
         <v>213954.39</v>
       </c>
       <c r="C36" s="13">
-        <v>51376.18</v>
+        <v>42951.2</v>
       </c>
       <c r="D36" s="13">
         <v>0</v>
       </c>
       <c r="E36" s="13">
-        <v>0</v>
+        <v>256905.59</v>
       </c>
       <c r="F36" s="13">
-        <v>265330.57</v>
+        <v>0</v>
       </c>
       <c r="G36" s="13">
-        <v>24734.28</v>
+        <v>0</v>
       </c>
       <c r="H36" s="13">
-        <v>4530227.66</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
@@ -6768,22 +6768,22 @@
         <v>340352.29</v>
       </c>
       <c r="C37" s="13">
-        <v>51376.19</v>
+        <v>42951.2</v>
       </c>
       <c r="D37" s="13">
         <v>0</v>
       </c>
       <c r="E37" s="13">
-        <v>0</v>
+        <v>383303.49</v>
       </c>
       <c r="F37" s="13">
-        <v>391728.48</v>
+        <v>0</v>
       </c>
       <c r="G37" s="13">
-        <v>26426.33</v>
+        <v>0</v>
       </c>
       <c r="H37" s="13">
-        <v>4948382.47</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
@@ -6794,22 +6794,22 @@
         <v>443555.75</v>
       </c>
       <c r="C38" s="13">
-        <v>51376.18</v>
+        <v>42951.19</v>
       </c>
       <c r="D38" s="13">
         <v>0</v>
       </c>
       <c r="E38" s="13">
-        <v>0</v>
+        <v>427468.96</v>
       </c>
       <c r="F38" s="13">
-        <v>494931.93</v>
+        <v>59037.98</v>
       </c>
       <c r="G38" s="13">
-        <v>28865.56</v>
+        <v>0</v>
       </c>
       <c r="H38" s="13">
-        <v>5472179.96</v>
+        <v>59037.98</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
@@ -6820,7 +6820,7 @@
         <v>516531.6</v>
       </c>
       <c r="C39" s="13">
-        <v>51376.2</v>
+        <v>42951.21</v>
       </c>
       <c r="D39" s="13">
         <v>0</v>
@@ -6829,13 +6829,13 @@
         <v>0</v>
       </c>
       <c r="F39" s="13">
-        <v>567907.8</v>
+        <v>559482.81</v>
       </c>
       <c r="G39" s="13">
-        <v>31921.05</v>
+        <v>344.39</v>
       </c>
       <c r="H39" s="13">
-        <v>6072008.81</v>
+        <v>618865.18</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
@@ -6846,7 +6846,7 @@
         <v>554306.68</v>
       </c>
       <c r="C40" s="13">
-        <v>51376.16</v>
+        <v>42951.17</v>
       </c>
       <c r="D40" s="13">
         <v>0</v>
@@ -6855,13 +6855,13 @@
         <v>0</v>
       </c>
       <c r="F40" s="13">
-        <v>605682.84</v>
+        <v>597257.85</v>
       </c>
       <c r="G40" s="13">
-        <v>35420.05</v>
+        <v>3610.05</v>
       </c>
       <c r="H40" s="13">
-        <v>6713111.7</v>
+        <v>1219733.08</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
@@ -6872,7 +6872,7 @@
         <v>554306.68</v>
       </c>
       <c r="C41" s="13">
-        <v>51376.2</v>
+        <v>42951.21</v>
       </c>
       <c r="D41" s="13">
         <v>0</v>
@@ -6881,13 +6881,13 @@
         <v>0</v>
       </c>
       <c r="F41" s="13">
-        <v>605682.88</v>
+        <v>597257.89</v>
       </c>
       <c r="G41" s="13">
-        <v>39159.82</v>
+        <v>7115.11</v>
       </c>
       <c r="H41" s="13">
-        <v>7357954.4</v>
+        <v>1824106.08</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
@@ -6898,7 +6898,7 @@
         <v>516531.57</v>
       </c>
       <c r="C42" s="13">
-        <v>51376.16</v>
+        <v>42951.17</v>
       </c>
       <c r="D42" s="13">
         <v>0</v>
@@ -6907,13 +6907,13 @@
         <v>0</v>
       </c>
       <c r="F42" s="13">
-        <v>567907.73</v>
+        <v>559482.74</v>
       </c>
       <c r="G42" s="13">
-        <v>42921.4</v>
+        <v>10640.62</v>
       </c>
       <c r="H42" s="13">
-        <v>7968783.53</v>
+        <v>2394229.44</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
@@ -6924,7 +6924,7 @@
         <v>443555.78</v>
       </c>
       <c r="C43" s="13">
-        <v>51376.2</v>
+        <v>42951.21</v>
       </c>
       <c r="D43" s="13">
         <v>0</v>
@@ -6933,13 +6933,13 @@
         <v>0</v>
       </c>
       <c r="F43" s="13">
-        <v>494931.98</v>
+        <v>486506.99</v>
       </c>
       <c r="G43" s="13">
-        <v>46484.57</v>
+        <v>13966.34</v>
       </c>
       <c r="H43" s="13">
-        <v>8510200.08</v>
+        <v>2894702.77</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
@@ -6950,7 +6950,7 @@
         <v>340352.29</v>
       </c>
       <c r="C44" s="13">
-        <v>51376.19</v>
+        <v>42951.21</v>
       </c>
       <c r="D44" s="13">
         <v>0</v>
@@ -6959,13 +6959,13 @@
         <v>0</v>
       </c>
       <c r="F44" s="13">
-        <v>391728.48</v>
+        <v>383303.5</v>
       </c>
       <c r="G44" s="13">
-        <v>49642.83</v>
+        <v>16885.77</v>
       </c>
       <c r="H44" s="13">
-        <v>8951571.39</v>
+        <v>3294892.04</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.25">
@@ -6976,7 +6976,7 @@
         <v>213954.38</v>
       </c>
       <c r="C45" s="13">
-        <v>51376.13</v>
+        <v>42951.14</v>
       </c>
       <c r="D45" s="13">
         <v>0</v>
@@ -6985,13 +6985,13 @@
         <v>0</v>
       </c>
       <c r="F45" s="13">
-        <v>265330.51</v>
+        <v>256905.52</v>
       </c>
       <c r="G45" s="13">
-        <v>52217.5</v>
+        <v>19220.2</v>
       </c>
       <c r="H45" s="13">
-        <v>9269119.4</v>
+        <v>3571017.76</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
@@ -7002,7 +7002,7 @@
         <v>72975.89</v>
       </c>
       <c r="C46" s="13">
-        <v>51376.19</v>
+        <v>42951.21</v>
       </c>
       <c r="D46" s="13">
         <v>0</v>
@@ -7011,13 +7011,13 @@
         <v>0</v>
       </c>
       <c r="F46" s="13">
-        <v>124352.08</v>
+        <v>115927.1</v>
       </c>
       <c r="G46" s="13">
-        <v>54069.86</v>
+        <v>20830.94</v>
       </c>
       <c r="H46" s="13">
-        <v>9447541.34</v>
+        <v>3707775.8</v>
       </c>
     </row>
   </sheetData>
